--- a/artfynd/A 7554-2023 artfynd.xlsx
+++ b/artfynd/A 7554-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 7554-2023 artfynd.xlsx
+++ b/artfynd/A 7554-2023 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>56197435</v>
       </c>
       <c r="B2" t="n">
-        <v>101120</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103683</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>468917.1691443076</v>
+        <v>468917</v>
       </c>
       <c r="R2" t="n">
-        <v>6216399.077352222</v>
+        <v>6216399</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2015-06-02</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2015-06-02</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -800,12 +785,7 @@
         <v>56197439</v>
       </c>
       <c r="B3" t="n">
-        <v>101325</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104255</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -837,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>469004.1676097864</v>
+        <v>469004</v>
       </c>
       <c r="R3" t="n">
-        <v>6216294.141919228</v>
+        <v>6216294</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,19 +850,9 @@
           <t>2015-06-02</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2015-06-02</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -922,12 +892,7 @@
         <v>56197441</v>
       </c>
       <c r="B4" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -959,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>469031.1534877336</v>
+        <v>469031</v>
       </c>
       <c r="R4" t="n">
-        <v>6216393.233974335</v>
+        <v>6216393</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,19 +957,9 @@
           <t>2015-06-02</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2015-06-02</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">

--- a/artfynd/A 7554-2023 artfynd.xlsx
+++ b/artfynd/A 7554-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56197435</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56197439</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,8 +1008,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56197441</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>